--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +70 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +90 €/mois.</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>1598</v>
+        <v>1621.67</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>63/100</t>
+          <t>64/100</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>220 000 € 5 500 €/m² Pro Autre · 40 m² Saint-Blaise Paris 75020 Voir l'annonce</t>
+          <t>3 nouvelles annonces dans votre zone personnalisée : Paris Votre recherche : Vente &gt; Boutique, Local commercial &gt; Paris &gt; Maximum 300,000 € 84 000 € Hôtel / Restaurant 38 m² Paris 20ème arrondissement (75020) Groupe POINTdeVENTE Voir l'annonce 178 000 € Hôtel / Restaurant 65 m² Vallée de Fécamp, Paris 12ème arrondissement (75012) KAPITOL IMMOBILIER Voir l'annonce 212 800 € Hôtel / Restaurant 70 m²</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
+++ b/docs/dossiers/dossier-saint-blaise-paris-b5fb461f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>localisation_incoherente · loyer_estime</t>
+          <t>localisation_incoherente · loyer_estime · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
